--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/21,09,26 Останкино КИ и ЗПФ/машина САП 27,09 ПРС_Донецк КИ/Заказ ЛП ПРС 27,09,26.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/21,09,26 Останкино КИ и ЗПФ/машина САП 27,09 ПРС_Донецк КИ/Заказ ЛП ПРС 27,09,26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\машина САП 27,09 ПРС_Донецк КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\21,09,26 Останкино КИ и ЗПФ\машина САП 27,09 ПРС_Донецк КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7FC2D9-F170-4239-8834-85FBAF4A3ED2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99A945B-ACF5-41DB-BF8B-8848032575A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
